--- a/public/templates/base.xlsx
+++ b/public/templates/base.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\braul\OneDrive\Escritorio\contract-processor\public\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A251EBF5-2F81-43F4-A906-DA7B526FDB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -49,23 +58,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -73,42 +85,49 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -298,31 +317,32 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10.71"/>
-    <col customWidth="1" min="3" max="3" width="21.29"/>
-    <col customWidth="1" min="4" max="4" width="12.86"/>
-    <col customWidth="1" min="5" max="5" width="10.71"/>
-    <col customWidth="1" min="6" max="6" width="12.43"/>
-    <col customWidth="1" min="7" max="7" width="10.71"/>
-    <col customWidth="1" min="8" max="8" width="12.71"/>
-    <col customWidth="1" min="9" max="9" width="14.29"/>
-    <col customWidth="1" min="10" max="10" width="13.0"/>
-    <col customWidth="1" min="11" max="11" width="17.29"/>
-    <col customWidth="1" min="12" max="26" width="10.71"/>
+    <col min="1" max="1" width="10.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" customWidth="1"/>
+    <col min="12" max="26" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -356,3388 +376,3386 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="2"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="2"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="2"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="2"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="2"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="2"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="2"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="2"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="2"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="2"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="2"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="2"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="2"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="2"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="2"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="2"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="2"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="2"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="2"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="2"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="2"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="2"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="2"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="2"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="2"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="2"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="2"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="2"/>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="2"/>
       <c r="E36" s="3"/>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="2"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="2"/>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="2"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="2"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="2"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="2"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="2"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C44" s="2"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="2"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46" s="2"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="2"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="2"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C49" s="2"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="2"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="2"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C52" s="2"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="2"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C54" s="2"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C55" s="2"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C56" s="2"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C57" s="2"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
+    <row r="58" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="2"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" ht="14.25" customHeight="1">
+    <row r="59" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="2"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" ht="14.25" customHeight="1">
+    <row r="60" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C60" s="2"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" ht="14.25" customHeight="1">
+    <row r="61" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C61" s="2"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
+    <row r="62" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="2"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" ht="14.25" customHeight="1">
+    <row r="63" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="2"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" ht="14.25" customHeight="1">
+    <row r="64" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C64" s="2"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" ht="14.25" customHeight="1">
+    <row r="65" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="2"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" ht="14.25" customHeight="1">
+    <row r="66" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C66" s="2"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" ht="14.25" customHeight="1">
+    <row r="67" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="2"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="2"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="2"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" ht="14.25" customHeight="1">
+    <row r="70" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C70" s="2"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C71" s="2"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
+    <row r="72" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="2"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
+    <row r="73" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="2"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C74" s="2"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="2"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="2"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C77" s="2"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C78" s="2"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C79" s="2"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C80" s="2"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C81" s="2"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C82" s="2"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C83" s="2"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C84" s="2"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C85" s="2"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C86" s="2"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C87" s="2"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C88" s="2"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C89" s="2"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="2"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C91" s="2"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="2"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="2"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1">
+    <row r="94" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C94" s="2"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="2"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="2"/>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="2"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1">
+    <row r="98" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="2"/>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1">
+    <row r="99" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C99" s="2"/>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1">
+    <row r="100" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C100" s="2"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
+    <row r="101" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C101" s="2"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1">
+    <row r="102" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="2"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
+    <row r="103" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C103" s="2"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1">
+    <row r="104" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C104" s="2"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1">
+    <row r="105" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C105" s="2"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
+    <row r="106" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C106" s="2"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C107" s="2"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1">
+    <row r="108" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C108" s="2"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1">
+    <row r="109" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C109" s="2"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1">
+    <row r="110" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C110" s="2"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1">
+    <row r="111" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C111" s="2"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C112" s="2"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1">
+    <row r="113" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="2"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C114" s="2"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1">
+    <row r="115" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="2"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1">
+    <row r="116" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="2"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
+    <row r="117" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="2"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1">
+    <row r="118" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="2"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
+    <row r="119" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C119" s="2"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
+    <row r="120" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="2"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
+    <row r="121" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C121" s="2"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="2"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
+    <row r="123" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C123" s="2"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
+    <row r="124" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C124" s="2"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
+    <row r="125" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C125" s="2"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C126" s="2"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C127" s="2"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C128" s="2"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C129" s="2"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C130" s="2"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
+    <row r="131" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="2"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C132" s="2"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
+    <row r="133" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C133" s="2"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C134" s="2"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
+    <row r="135" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C135" s="2"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
+    <row r="136" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C136" s="2"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
+    <row r="137" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="2"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
+    <row r="138" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="2"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
+    <row r="139" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C139" s="2"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="2"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
+    <row r="141" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="2"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
+    <row r="142" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C142" s="2"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
+    <row r="143" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C143" s="2"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
+    <row r="144" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C144" s="2"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
+    <row r="145" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C145" s="2"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
+    <row r="146" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="2"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
+    <row r="147" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="2"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
+    <row r="148" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C148" s="2"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
+    <row r="149" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C149" s="2"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
+    <row r="150" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C150" s="2"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
+    <row r="151" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C151" s="2"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1">
+    <row r="152" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C152" s="2"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1">
+    <row r="153" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C153" s="2"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
+    <row r="154" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C154" s="2"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
+    <row r="155" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C155" s="2"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1">
+    <row r="156" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C156" s="2"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
+    <row r="157" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C157" s="2"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1">
+    <row r="158" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C158" s="2"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1">
+    <row r="159" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C159" s="2"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1">
+    <row r="160" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C160" s="2"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
+    <row r="161" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C161" s="2"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1">
+    <row r="162" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C162" s="2"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1">
+    <row r="163" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C163" s="2"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
+    <row r="164" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C164" s="2"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
+    <row r="165" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C165" s="2"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1">
+    <row r="166" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C166" s="2"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C167" s="2"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1">
+    <row r="168" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C168" s="2"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1">
+    <row r="169" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C169" s="2"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1">
+    <row r="170" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C170" s="2"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1">
+    <row r="171" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C171" s="2"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1">
+    <row r="172" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C172" s="2"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1">
+    <row r="173" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C173" s="2"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1">
+    <row r="174" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C174" s="2"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1">
+    <row r="175" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C175" s="2"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1">
+    <row r="176" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C176" s="2"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1">
+    <row r="177" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C177" s="2"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1">
+    <row r="178" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C178" s="2"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1">
+    <row r="179" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C179" s="2"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1">
+    <row r="180" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C180" s="2"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1">
+    <row r="181" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C181" s="2"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1">
+    <row r="182" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C182" s="2"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1">
+    <row r="183" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C183" s="2"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1">
+    <row r="184" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C184" s="2"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1">
+    <row r="185" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C185" s="2"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1">
+    <row r="186" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C186" s="2"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1">
+    <row r="187" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C187" s="2"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1">
+    <row r="188" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C188" s="2"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1">
+    <row r="189" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C189" s="2"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1">
+    <row r="190" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C190" s="2"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1">
+    <row r="191" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C191" s="2"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1">
+    <row r="192" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C192" s="2"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1">
+    <row r="193" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C193" s="2"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1">
+    <row r="194" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C194" s="2"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1">
+    <row r="195" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C195" s="2"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1">
+    <row r="196" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C196" s="2"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1">
+    <row r="197" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C197" s="2"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1">
+    <row r="198" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C198" s="2"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1">
+    <row r="199" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C199" s="2"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1">
+    <row r="200" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C200" s="2"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1">
+    <row r="201" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C201" s="2"/>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1">
+    <row r="202" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C202" s="2"/>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1">
+    <row r="203" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C203" s="2"/>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1">
+    <row r="204" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C204" s="2"/>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1">
+    <row r="205" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C205" s="2"/>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1">
+    <row r="206" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C206" s="2"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1">
+    <row r="207" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C207" s="2"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1">
+    <row r="208" spans="3:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C208" s="2"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1">
+    <row r="209" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C209" s="2"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1">
+    <row r="210" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C210" s="2"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1">
+    <row r="211" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C211" s="2"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1">
+    <row r="212" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C212" s="2"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1">
+    <row r="213" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C213" s="2"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1">
+    <row r="214" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C214" s="2"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1">
+    <row r="215" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C215" s="2"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1">
+    <row r="216" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C216" s="2"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1">
+    <row r="217" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C217" s="2"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1">
+    <row r="218" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C218" s="2"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1">
+    <row r="219" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C219" s="2"/>
     </row>
-    <row r="220" ht="14.25" customHeight="1">
+    <row r="220" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C220" s="2"/>
     </row>
-    <row r="221" ht="14.25" customHeight="1">
+    <row r="221" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C221" s="2"/>
     </row>
-    <row r="222" ht="14.25" customHeight="1">
+    <row r="222" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C222" s="2"/>
     </row>
-    <row r="223" ht="14.25" customHeight="1">
+    <row r="223" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C223" s="2"/>
     </row>
-    <row r="224" ht="14.25" customHeight="1">
+    <row r="224" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C224" s="2"/>
     </row>
-    <row r="225" ht="14.25" customHeight="1">
+    <row r="225" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C225" s="2"/>
     </row>
-    <row r="226" ht="14.25" customHeight="1">
+    <row r="226" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C226" s="2"/>
     </row>
-    <row r="227" ht="14.25" customHeight="1">
+    <row r="227" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C227" s="2"/>
     </row>
-    <row r="228" ht="14.25" customHeight="1">
+    <row r="228" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C228" s="2"/>
     </row>
-    <row r="229" ht="14.25" customHeight="1">
+    <row r="229" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C229" s="2"/>
     </row>
-    <row r="230" ht="14.25" customHeight="1">
+    <row r="230" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C230" s="2"/>
     </row>
-    <row r="231" ht="14.25" customHeight="1">
+    <row r="231" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C231" s="2"/>
     </row>
-    <row r="232" ht="14.25" customHeight="1">
+    <row r="232" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C232" s="2"/>
     </row>
-    <row r="233" ht="14.25" customHeight="1">
+    <row r="233" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C233" s="2"/>
     </row>
-    <row r="234" ht="14.25" customHeight="1">
+    <row r="234" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C234" s="2"/>
     </row>
-    <row r="235" ht="14.25" customHeight="1">
+    <row r="235" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C235" s="2"/>
     </row>
-    <row r="236" ht="14.25" customHeight="1">
+    <row r="236" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C236" s="2"/>
     </row>
-    <row r="237" ht="14.25" customHeight="1">
+    <row r="237" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C237" s="2"/>
     </row>
-    <row r="238" ht="14.25" customHeight="1">
+    <row r="238" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C238" s="2"/>
     </row>
-    <row r="239" ht="14.25" customHeight="1">
+    <row r="239" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C239" s="2"/>
     </row>
-    <row r="240" ht="14.25" customHeight="1">
+    <row r="240" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C240" s="2"/>
     </row>
-    <row r="241" ht="14.25" customHeight="1">
+    <row r="241" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C241" s="2"/>
     </row>
-    <row r="242" ht="14.25" customHeight="1">
+    <row r="242" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C242" s="2"/>
     </row>
-    <row r="243" ht="14.25" customHeight="1">
+    <row r="243" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C243" s="2"/>
     </row>
-    <row r="244" ht="14.25" customHeight="1">
+    <row r="244" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C244" s="2"/>
     </row>
-    <row r="245" ht="14.25" customHeight="1">
+    <row r="245" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C245" s="2"/>
     </row>
-    <row r="246" ht="14.25" customHeight="1">
+    <row r="246" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C246" s="2"/>
     </row>
-    <row r="247" ht="14.25" customHeight="1">
+    <row r="247" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C247" s="2"/>
     </row>
-    <row r="248" ht="14.25" customHeight="1">
+    <row r="248" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C248" s="2"/>
     </row>
-    <row r="249" ht="14.25" customHeight="1">
+    <row r="249" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C249" s="2"/>
     </row>
-    <row r="250" ht="14.25" customHeight="1">
+    <row r="250" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C250" s="2"/>
     </row>
-    <row r="251" ht="14.25" customHeight="1">
+    <row r="251" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C251" s="2"/>
     </row>
-    <row r="252" ht="14.25" customHeight="1">
+    <row r="252" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C252" s="2"/>
     </row>
-    <row r="253" ht="14.25" customHeight="1">
+    <row r="253" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C253" s="2"/>
     </row>
-    <row r="254" ht="14.25" customHeight="1">
+    <row r="254" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C254" s="2"/>
     </row>
-    <row r="255" ht="14.25" customHeight="1">
+    <row r="255" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C255" s="2"/>
     </row>
-    <row r="256" ht="14.25" customHeight="1">
+    <row r="256" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C256" s="2"/>
     </row>
-    <row r="257" ht="14.25" customHeight="1">
+    <row r="257" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C257" s="2"/>
     </row>
-    <row r="258" ht="14.25" customHeight="1">
+    <row r="258" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C258" s="2"/>
     </row>
-    <row r="259" ht="14.25" customHeight="1">
+    <row r="259" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C259" s="2"/>
     </row>
-    <row r="260" ht="14.25" customHeight="1">
+    <row r="260" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C260" s="2"/>
     </row>
-    <row r="261" ht="14.25" customHeight="1">
+    <row r="261" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C261" s="2"/>
     </row>
-    <row r="262" ht="14.25" customHeight="1">
+    <row r="262" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C262" s="2"/>
     </row>
-    <row r="263" ht="14.25" customHeight="1">
+    <row r="263" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C263" s="2"/>
     </row>
-    <row r="264" ht="14.25" customHeight="1">
+    <row r="264" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C264" s="2"/>
     </row>
-    <row r="265" ht="14.25" customHeight="1">
+    <row r="265" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C265" s="2"/>
     </row>
-    <row r="266" ht="14.25" customHeight="1">
+    <row r="266" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C266" s="2"/>
     </row>
-    <row r="267" ht="14.25" customHeight="1">
+    <row r="267" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C267" s="2"/>
     </row>
-    <row r="268" ht="14.25" customHeight="1">
+    <row r="268" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C268" s="2"/>
     </row>
-    <row r="269" ht="14.25" customHeight="1">
+    <row r="269" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C269" s="2"/>
     </row>
-    <row r="270" ht="14.25" customHeight="1">
+    <row r="270" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C270" s="2"/>
     </row>
-    <row r="271" ht="14.25" customHeight="1">
+    <row r="271" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C271" s="2"/>
     </row>
-    <row r="272" ht="14.25" customHeight="1">
+    <row r="272" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C272" s="2"/>
     </row>
-    <row r="273" ht="14.25" customHeight="1">
+    <row r="273" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C273" s="2"/>
     </row>
-    <row r="274" ht="14.25" customHeight="1">
+    <row r="274" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C274" s="2"/>
     </row>
-    <row r="275" ht="14.25" customHeight="1">
+    <row r="275" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C275" s="2"/>
     </row>
-    <row r="276" ht="14.25" customHeight="1">
+    <row r="276" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C276" s="2"/>
     </row>
-    <row r="277" ht="14.25" customHeight="1">
+    <row r="277" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C277" s="2"/>
     </row>
-    <row r="278" ht="14.25" customHeight="1">
+    <row r="278" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C278" s="2"/>
     </row>
-    <row r="279" ht="14.25" customHeight="1">
+    <row r="279" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C279" s="2"/>
     </row>
-    <row r="280" ht="14.25" customHeight="1">
+    <row r="280" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C280" s="2"/>
     </row>
-    <row r="281" ht="14.25" customHeight="1">
+    <row r="281" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C281" s="2"/>
     </row>
-    <row r="282" ht="14.25" customHeight="1">
+    <row r="282" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C282" s="2"/>
     </row>
-    <row r="283" ht="14.25" customHeight="1">
+    <row r="283" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C283" s="2"/>
     </row>
-    <row r="284" ht="14.25" customHeight="1">
+    <row r="284" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C284" s="2"/>
     </row>
-    <row r="285" ht="14.25" customHeight="1">
+    <row r="285" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C285" s="2"/>
     </row>
-    <row r="286" ht="14.25" customHeight="1">
+    <row r="286" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C286" s="2"/>
     </row>
-    <row r="287" ht="14.25" customHeight="1">
+    <row r="287" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C287" s="2"/>
     </row>
-    <row r="288" ht="14.25" customHeight="1">
+    <row r="288" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C288" s="2"/>
     </row>
-    <row r="289" ht="14.25" customHeight="1">
+    <row r="289" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C289" s="2"/>
     </row>
-    <row r="290" ht="14.25" customHeight="1">
+    <row r="290" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C290" s="2"/>
     </row>
-    <row r="291" ht="14.25" customHeight="1">
+    <row r="291" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C291" s="2"/>
     </row>
-    <row r="292" ht="14.25" customHeight="1">
+    <row r="292" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C292" s="2"/>
     </row>
-    <row r="293" ht="14.25" customHeight="1">
+    <row r="293" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C293" s="2"/>
     </row>
-    <row r="294" ht="14.25" customHeight="1">
+    <row r="294" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C294" s="2"/>
     </row>
-    <row r="295" ht="14.25" customHeight="1">
+    <row r="295" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C295" s="2"/>
     </row>
-    <row r="296" ht="14.25" customHeight="1">
+    <row r="296" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C296" s="2"/>
     </row>
-    <row r="297" ht="14.25" customHeight="1">
+    <row r="297" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C297" s="2"/>
     </row>
-    <row r="298" ht="14.25" customHeight="1">
+    <row r="298" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C298" s="2"/>
     </row>
-    <row r="299" ht="14.25" customHeight="1">
+    <row r="299" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C299" s="2"/>
     </row>
-    <row r="300" ht="14.25" customHeight="1">
+    <row r="300" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C300" s="2"/>
     </row>
-    <row r="301" ht="14.25" customHeight="1">
+    <row r="301" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C301" s="2"/>
     </row>
-    <row r="302" ht="14.25" customHeight="1">
+    <row r="302" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C302" s="2"/>
     </row>
-    <row r="303" ht="14.25" customHeight="1">
+    <row r="303" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C303" s="2"/>
     </row>
-    <row r="304" ht="14.25" customHeight="1">
+    <row r="304" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C304" s="2"/>
     </row>
-    <row r="305" ht="14.25" customHeight="1">
+    <row r="305" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C305" s="2"/>
     </row>
-    <row r="306" ht="14.25" customHeight="1">
+    <row r="306" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C306" s="2"/>
     </row>
-    <row r="307" ht="14.25" customHeight="1">
+    <row r="307" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C307" s="2"/>
     </row>
-    <row r="308" ht="14.25" customHeight="1">
+    <row r="308" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C308" s="2"/>
     </row>
-    <row r="309" ht="14.25" customHeight="1">
+    <row r="309" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C309" s="2"/>
     </row>
-    <row r="310" ht="14.25" customHeight="1">
+    <row r="310" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C310" s="2"/>
     </row>
-    <row r="311" ht="14.25" customHeight="1">
+    <row r="311" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C311" s="2"/>
     </row>
-    <row r="312" ht="14.25" customHeight="1">
+    <row r="312" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C312" s="2"/>
     </row>
-    <row r="313" ht="14.25" customHeight="1">
+    <row r="313" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C313" s="2"/>
     </row>
-    <row r="314" ht="14.25" customHeight="1">
+    <row r="314" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C314" s="2"/>
     </row>
-    <row r="315" ht="14.25" customHeight="1">
+    <row r="315" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C315" s="2"/>
     </row>
-    <row r="316" ht="14.25" customHeight="1">
+    <row r="316" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C316" s="2"/>
     </row>
-    <row r="317" ht="14.25" customHeight="1">
+    <row r="317" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C317" s="2"/>
     </row>
-    <row r="318" ht="14.25" customHeight="1">
+    <row r="318" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C318" s="2"/>
     </row>
-    <row r="319" ht="14.25" customHeight="1">
+    <row r="319" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C319" s="2"/>
     </row>
-    <row r="320" ht="14.25" customHeight="1">
+    <row r="320" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C320" s="2"/>
     </row>
-    <row r="321" ht="14.25" customHeight="1">
+    <row r="321" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C321" s="2"/>
     </row>
-    <row r="322" ht="14.25" customHeight="1">
+    <row r="322" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C322" s="2"/>
     </row>
-    <row r="323" ht="14.25" customHeight="1">
+    <row r="323" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C323" s="2"/>
     </row>
-    <row r="324" ht="14.25" customHeight="1">
+    <row r="324" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C324" s="2"/>
     </row>
-    <row r="325" ht="14.25" customHeight="1">
+    <row r="325" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C325" s="2"/>
     </row>
-    <row r="326" ht="14.25" customHeight="1">
+    <row r="326" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C326" s="2"/>
     </row>
-    <row r="327" ht="14.25" customHeight="1">
+    <row r="327" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C327" s="2"/>
     </row>
-    <row r="328" ht="14.25" customHeight="1">
+    <row r="328" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C328" s="2"/>
     </row>
-    <row r="329" ht="14.25" customHeight="1">
+    <row r="329" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C329" s="2"/>
     </row>
-    <row r="330" ht="14.25" customHeight="1">
+    <row r="330" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C330" s="2"/>
     </row>
-    <row r="331" ht="14.25" customHeight="1">
+    <row r="331" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C331" s="2"/>
     </row>
-    <row r="332" ht="14.25" customHeight="1">
+    <row r="332" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C332" s="2"/>
     </row>
-    <row r="333" ht="14.25" customHeight="1">
+    <row r="333" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C333" s="2"/>
     </row>
-    <row r="334" ht="14.25" customHeight="1">
+    <row r="334" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C334" s="2"/>
     </row>
-    <row r="335" ht="14.25" customHeight="1">
+    <row r="335" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C335" s="2"/>
     </row>
-    <row r="336" ht="14.25" customHeight="1">
+    <row r="336" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C336" s="2"/>
     </row>
-    <row r="337" ht="14.25" customHeight="1">
+    <row r="337" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C337" s="2"/>
     </row>
-    <row r="338" ht="14.25" customHeight="1">
+    <row r="338" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C338" s="2"/>
     </row>
-    <row r="339" ht="14.25" customHeight="1">
+    <row r="339" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C339" s="2"/>
     </row>
-    <row r="340" ht="14.25" customHeight="1">
+    <row r="340" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C340" s="2"/>
     </row>
-    <row r="341" ht="14.25" customHeight="1">
+    <row r="341" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C341" s="2"/>
     </row>
-    <row r="342" ht="14.25" customHeight="1">
+    <row r="342" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C342" s="2"/>
     </row>
-    <row r="343" ht="14.25" customHeight="1">
+    <row r="343" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C343" s="2"/>
     </row>
-    <row r="344" ht="14.25" customHeight="1">
+    <row r="344" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C344" s="2"/>
     </row>
-    <row r="345" ht="14.25" customHeight="1">
+    <row r="345" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C345" s="2"/>
     </row>
-    <row r="346" ht="14.25" customHeight="1">
+    <row r="346" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C346" s="2"/>
     </row>
-    <row r="347" ht="14.25" customHeight="1">
+    <row r="347" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C347" s="2"/>
     </row>
-    <row r="348" ht="14.25" customHeight="1">
+    <row r="348" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C348" s="2"/>
     </row>
-    <row r="349" ht="14.25" customHeight="1">
+    <row r="349" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C349" s="2"/>
     </row>
-    <row r="350" ht="14.25" customHeight="1">
+    <row r="350" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C350" s="2"/>
     </row>
-    <row r="351" ht="14.25" customHeight="1">
+    <row r="351" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C351" s="2"/>
     </row>
-    <row r="352" ht="14.25" customHeight="1">
+    <row r="352" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C352" s="2"/>
     </row>
-    <row r="353" ht="14.25" customHeight="1">
+    <row r="353" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C353" s="2"/>
     </row>
-    <row r="354" ht="14.25" customHeight="1">
+    <row r="354" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C354" s="2"/>
     </row>
-    <row r="355" ht="14.25" customHeight="1">
+    <row r="355" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C355" s="2"/>
     </row>
-    <row r="356" ht="14.25" customHeight="1">
+    <row r="356" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C356" s="2"/>
     </row>
-    <row r="357" ht="14.25" customHeight="1">
+    <row r="357" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C357" s="2"/>
     </row>
-    <row r="358" ht="14.25" customHeight="1">
+    <row r="358" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C358" s="2"/>
     </row>
-    <row r="359" ht="14.25" customHeight="1">
+    <row r="359" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C359" s="2"/>
     </row>
-    <row r="360" ht="14.25" customHeight="1">
+    <row r="360" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C360" s="2"/>
     </row>
-    <row r="361" ht="14.25" customHeight="1">
+    <row r="361" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C361" s="2"/>
     </row>
-    <row r="362" ht="14.25" customHeight="1">
+    <row r="362" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C362" s="2"/>
     </row>
-    <row r="363" ht="14.25" customHeight="1">
+    <row r="363" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C363" s="2"/>
     </row>
-    <row r="364" ht="14.25" customHeight="1">
+    <row r="364" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C364" s="2"/>
     </row>
-    <row r="365" ht="14.25" customHeight="1">
+    <row r="365" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C365" s="2"/>
     </row>
-    <row r="366" ht="14.25" customHeight="1">
+    <row r="366" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C366" s="2"/>
     </row>
-    <row r="367" ht="14.25" customHeight="1">
+    <row r="367" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C367" s="2"/>
     </row>
-    <row r="368" ht="14.25" customHeight="1">
+    <row r="368" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C368" s="2"/>
     </row>
-    <row r="369" ht="14.25" customHeight="1">
+    <row r="369" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C369" s="2"/>
     </row>
-    <row r="370" ht="14.25" customHeight="1">
+    <row r="370" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C370" s="2"/>
     </row>
-    <row r="371" ht="14.25" customHeight="1">
+    <row r="371" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C371" s="2"/>
     </row>
-    <row r="372" ht="14.25" customHeight="1">
+    <row r="372" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C372" s="2"/>
     </row>
-    <row r="373" ht="14.25" customHeight="1">
+    <row r="373" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C373" s="2"/>
     </row>
-    <row r="374" ht="14.25" customHeight="1">
+    <row r="374" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C374" s="2"/>
     </row>
-    <row r="375" ht="14.25" customHeight="1">
+    <row r="375" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C375" s="2"/>
     </row>
-    <row r="376" ht="14.25" customHeight="1">
+    <row r="376" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C376" s="2"/>
     </row>
-    <row r="377" ht="14.25" customHeight="1">
+    <row r="377" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C377" s="2"/>
     </row>
-    <row r="378" ht="14.25" customHeight="1">
+    <row r="378" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C378" s="2"/>
     </row>
-    <row r="379" ht="14.25" customHeight="1">
+    <row r="379" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C379" s="2"/>
     </row>
-    <row r="380" ht="14.25" customHeight="1">
+    <row r="380" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C380" s="2"/>
     </row>
-    <row r="381" ht="14.25" customHeight="1">
+    <row r="381" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C381" s="2"/>
     </row>
-    <row r="382" ht="14.25" customHeight="1">
+    <row r="382" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C382" s="2"/>
     </row>
-    <row r="383" ht="14.25" customHeight="1">
+    <row r="383" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C383" s="2"/>
     </row>
-    <row r="384" ht="14.25" customHeight="1">
+    <row r="384" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C384" s="2"/>
     </row>
-    <row r="385" ht="14.25" customHeight="1">
+    <row r="385" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C385" s="2"/>
     </row>
-    <row r="386" ht="14.25" customHeight="1">
+    <row r="386" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C386" s="2"/>
     </row>
-    <row r="387" ht="14.25" customHeight="1">
+    <row r="387" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C387" s="2"/>
     </row>
-    <row r="388" ht="14.25" customHeight="1">
+    <row r="388" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C388" s="2"/>
     </row>
-    <row r="389" ht="14.25" customHeight="1">
+    <row r="389" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C389" s="2"/>
     </row>
-    <row r="390" ht="14.25" customHeight="1">
+    <row r="390" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C390" s="2"/>
     </row>
-    <row r="391" ht="14.25" customHeight="1">
+    <row r="391" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C391" s="2"/>
     </row>
-    <row r="392" ht="14.25" customHeight="1">
+    <row r="392" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C392" s="2"/>
     </row>
-    <row r="393" ht="14.25" customHeight="1">
+    <row r="393" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C393" s="2"/>
     </row>
-    <row r="394" ht="14.25" customHeight="1">
+    <row r="394" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C394" s="2"/>
     </row>
-    <row r="395" ht="14.25" customHeight="1">
+    <row r="395" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C395" s="2"/>
     </row>
-    <row r="396" ht="14.25" customHeight="1">
+    <row r="396" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C396" s="2"/>
     </row>
-    <row r="397" ht="14.25" customHeight="1">
+    <row r="397" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C397" s="2"/>
     </row>
-    <row r="398" ht="14.25" customHeight="1">
+    <row r="398" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C398" s="2"/>
     </row>
-    <row r="399" ht="14.25" customHeight="1">
+    <row r="399" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C399" s="2"/>
     </row>
-    <row r="400" ht="14.25" customHeight="1">
+    <row r="400" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C400" s="2"/>
     </row>
-    <row r="401" ht="14.25" customHeight="1">
+    <row r="401" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C401" s="2"/>
     </row>
-    <row r="402" ht="14.25" customHeight="1">
+    <row r="402" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C402" s="2"/>
     </row>
-    <row r="403" ht="14.25" customHeight="1">
+    <row r="403" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C403" s="2"/>
     </row>
-    <row r="404" ht="14.25" customHeight="1">
+    <row r="404" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C404" s="2"/>
     </row>
-    <row r="405" ht="14.25" customHeight="1">
+    <row r="405" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C405" s="2"/>
     </row>
-    <row r="406" ht="14.25" customHeight="1">
+    <row r="406" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C406" s="2"/>
     </row>
-    <row r="407" ht="14.25" customHeight="1">
+    <row r="407" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C407" s="2"/>
     </row>
-    <row r="408" ht="14.25" customHeight="1">
+    <row r="408" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C408" s="2"/>
     </row>
-    <row r="409" ht="14.25" customHeight="1">
+    <row r="409" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C409" s="2"/>
     </row>
-    <row r="410" ht="14.25" customHeight="1">
+    <row r="410" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C410" s="2"/>
     </row>
-    <row r="411" ht="14.25" customHeight="1">
+    <row r="411" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C411" s="2"/>
     </row>
-    <row r="412" ht="14.25" customHeight="1">
+    <row r="412" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C412" s="2"/>
     </row>
-    <row r="413" ht="14.25" customHeight="1">
+    <row r="413" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C413" s="2"/>
     </row>
-    <row r="414" ht="14.25" customHeight="1">
+    <row r="414" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C414" s="2"/>
     </row>
-    <row r="415" ht="14.25" customHeight="1">
+    <row r="415" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C415" s="2"/>
     </row>
-    <row r="416" ht="14.25" customHeight="1">
+    <row r="416" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C416" s="2"/>
     </row>
-    <row r="417" ht="14.25" customHeight="1">
+    <row r="417" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C417" s="2"/>
     </row>
-    <row r="418" ht="14.25" customHeight="1">
+    <row r="418" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C418" s="2"/>
     </row>
-    <row r="419" ht="14.25" customHeight="1">
+    <row r="419" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C419" s="2"/>
     </row>
-    <row r="420" ht="14.25" customHeight="1">
+    <row r="420" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C420" s="2"/>
     </row>
-    <row r="421" ht="14.25" customHeight="1">
+    <row r="421" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C421" s="2"/>
     </row>
-    <row r="422" ht="14.25" customHeight="1">
+    <row r="422" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C422" s="2"/>
     </row>
-    <row r="423" ht="14.25" customHeight="1">
+    <row r="423" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C423" s="2"/>
     </row>
-    <row r="424" ht="14.25" customHeight="1">
+    <row r="424" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C424" s="2"/>
     </row>
-    <row r="425" ht="14.25" customHeight="1">
+    <row r="425" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C425" s="2"/>
     </row>
-    <row r="426" ht="14.25" customHeight="1">
+    <row r="426" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C426" s="2"/>
     </row>
-    <row r="427" ht="14.25" customHeight="1">
+    <row r="427" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C427" s="2"/>
     </row>
-    <row r="428" ht="14.25" customHeight="1">
+    <row r="428" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C428" s="2"/>
     </row>
-    <row r="429" ht="14.25" customHeight="1">
+    <row r="429" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C429" s="2"/>
     </row>
-    <row r="430" ht="14.25" customHeight="1">
+    <row r="430" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C430" s="2"/>
     </row>
-    <row r="431" ht="14.25" customHeight="1">
+    <row r="431" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C431" s="2"/>
     </row>
-    <row r="432" ht="14.25" customHeight="1">
+    <row r="432" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C432" s="2"/>
     </row>
-    <row r="433" ht="14.25" customHeight="1">
+    <row r="433" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C433" s="2"/>
     </row>
-    <row r="434" ht="14.25" customHeight="1">
+    <row r="434" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C434" s="2"/>
     </row>
-    <row r="435" ht="14.25" customHeight="1">
+    <row r="435" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C435" s="2"/>
     </row>
-    <row r="436" ht="14.25" customHeight="1">
+    <row r="436" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C436" s="2"/>
     </row>
-    <row r="437" ht="14.25" customHeight="1">
+    <row r="437" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C437" s="2"/>
     </row>
-    <row r="438" ht="14.25" customHeight="1">
+    <row r="438" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C438" s="2"/>
     </row>
-    <row r="439" ht="14.25" customHeight="1">
+    <row r="439" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C439" s="2"/>
     </row>
-    <row r="440" ht="14.25" customHeight="1">
+    <row r="440" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C440" s="2"/>
     </row>
-    <row r="441" ht="14.25" customHeight="1">
+    <row r="441" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C441" s="2"/>
     </row>
-    <row r="442" ht="14.25" customHeight="1">
+    <row r="442" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C442" s="2"/>
     </row>
-    <row r="443" ht="14.25" customHeight="1">
+    <row r="443" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C443" s="2"/>
     </row>
-    <row r="444" ht="14.25" customHeight="1">
+    <row r="444" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C444" s="2"/>
     </row>
-    <row r="445" ht="14.25" customHeight="1">
+    <row r="445" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C445" s="2"/>
     </row>
-    <row r="446" ht="14.25" customHeight="1">
+    <row r="446" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C446" s="2"/>
     </row>
-    <row r="447" ht="14.25" customHeight="1">
+    <row r="447" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C447" s="2"/>
     </row>
-    <row r="448" ht="14.25" customHeight="1">
+    <row r="448" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C448" s="2"/>
     </row>
-    <row r="449" ht="14.25" customHeight="1">
+    <row r="449" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C449" s="2"/>
     </row>
-    <row r="450" ht="14.25" customHeight="1">
+    <row r="450" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C450" s="2"/>
     </row>
-    <row r="451" ht="14.25" customHeight="1">
+    <row r="451" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C451" s="2"/>
     </row>
-    <row r="452" ht="14.25" customHeight="1">
+    <row r="452" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C452" s="2"/>
     </row>
-    <row r="453" ht="14.25" customHeight="1">
+    <row r="453" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C453" s="2"/>
     </row>
-    <row r="454" ht="14.25" customHeight="1">
+    <row r="454" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C454" s="2"/>
     </row>
-    <row r="455" ht="14.25" customHeight="1">
+    <row r="455" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C455" s="2"/>
     </row>
-    <row r="456" ht="14.25" customHeight="1">
+    <row r="456" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C456" s="2"/>
     </row>
-    <row r="457" ht="14.25" customHeight="1">
+    <row r="457" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C457" s="2"/>
     </row>
-    <row r="458" ht="14.25" customHeight="1">
+    <row r="458" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C458" s="2"/>
     </row>
-    <row r="459" ht="14.25" customHeight="1">
+    <row r="459" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C459" s="2"/>
     </row>
-    <row r="460" ht="14.25" customHeight="1">
+    <row r="460" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C460" s="2"/>
     </row>
-    <row r="461" ht="14.25" customHeight="1">
+    <row r="461" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C461" s="2"/>
     </row>
-    <row r="462" ht="14.25" customHeight="1">
+    <row r="462" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C462" s="2"/>
     </row>
-    <row r="463" ht="14.25" customHeight="1">
+    <row r="463" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C463" s="2"/>
     </row>
-    <row r="464" ht="14.25" customHeight="1">
+    <row r="464" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C464" s="2"/>
     </row>
-    <row r="465" ht="14.25" customHeight="1">
+    <row r="465" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C465" s="2"/>
     </row>
-    <row r="466" ht="14.25" customHeight="1">
+    <row r="466" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C466" s="2"/>
     </row>
-    <row r="467" ht="14.25" customHeight="1">
+    <row r="467" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C467" s="2"/>
     </row>
-    <row r="468" ht="14.25" customHeight="1">
+    <row r="468" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C468" s="2"/>
     </row>
-    <row r="469" ht="14.25" customHeight="1">
+    <row r="469" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C469" s="2"/>
     </row>
-    <row r="470" ht="14.25" customHeight="1">
+    <row r="470" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C470" s="2"/>
     </row>
-    <row r="471" ht="14.25" customHeight="1">
+    <row r="471" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C471" s="2"/>
     </row>
-    <row r="472" ht="14.25" customHeight="1">
+    <row r="472" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C472" s="2"/>
     </row>
-    <row r="473" ht="14.25" customHeight="1">
+    <row r="473" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C473" s="2"/>
     </row>
-    <row r="474" ht="14.25" customHeight="1">
+    <row r="474" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C474" s="2"/>
     </row>
-    <row r="475" ht="14.25" customHeight="1">
+    <row r="475" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C475" s="2"/>
     </row>
-    <row r="476" ht="14.25" customHeight="1">
+    <row r="476" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C476" s="2"/>
     </row>
-    <row r="477" ht="14.25" customHeight="1">
+    <row r="477" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C477" s="2"/>
     </row>
-    <row r="478" ht="14.25" customHeight="1">
+    <row r="478" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C478" s="2"/>
     </row>
-    <row r="479" ht="14.25" customHeight="1">
+    <row r="479" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C479" s="2"/>
     </row>
-    <row r="480" ht="14.25" customHeight="1">
+    <row r="480" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C480" s="2"/>
     </row>
-    <row r="481" ht="14.25" customHeight="1">
+    <row r="481" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C481" s="2"/>
     </row>
-    <row r="482" ht="14.25" customHeight="1">
+    <row r="482" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C482" s="2"/>
     </row>
-    <row r="483" ht="14.25" customHeight="1">
+    <row r="483" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C483" s="2"/>
     </row>
-    <row r="484" ht="14.25" customHeight="1">
+    <row r="484" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C484" s="2"/>
     </row>
-    <row r="485" ht="14.25" customHeight="1">
+    <row r="485" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C485" s="2"/>
     </row>
-    <row r="486" ht="14.25" customHeight="1">
+    <row r="486" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C486" s="2"/>
     </row>
-    <row r="487" ht="14.25" customHeight="1">
+    <row r="487" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C487" s="2"/>
     </row>
-    <row r="488" ht="14.25" customHeight="1">
+    <row r="488" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C488" s="2"/>
     </row>
-    <row r="489" ht="14.25" customHeight="1">
+    <row r="489" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C489" s="2"/>
     </row>
-    <row r="490" ht="14.25" customHeight="1">
+    <row r="490" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C490" s="2"/>
     </row>
-    <row r="491" ht="14.25" customHeight="1">
+    <row r="491" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C491" s="2"/>
     </row>
-    <row r="492" ht="14.25" customHeight="1">
+    <row r="492" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C492" s="2"/>
     </row>
-    <row r="493" ht="14.25" customHeight="1">
+    <row r="493" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C493" s="2"/>
     </row>
-    <row r="494" ht="14.25" customHeight="1">
+    <row r="494" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C494" s="2"/>
     </row>
-    <row r="495" ht="14.25" customHeight="1">
+    <row r="495" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C495" s="2"/>
     </row>
-    <row r="496" ht="14.25" customHeight="1">
+    <row r="496" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C496" s="2"/>
     </row>
-    <row r="497" ht="14.25" customHeight="1">
+    <row r="497" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C497" s="2"/>
     </row>
-    <row r="498" ht="14.25" customHeight="1">
+    <row r="498" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C498" s="2"/>
     </row>
-    <row r="499" ht="14.25" customHeight="1">
+    <row r="499" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C499" s="2"/>
     </row>
-    <row r="500" ht="14.25" customHeight="1">
+    <row r="500" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C500" s="2"/>
     </row>
-    <row r="501" ht="14.25" customHeight="1">
+    <row r="501" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C501" s="2"/>
     </row>
-    <row r="502" ht="14.25" customHeight="1">
+    <row r="502" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C502" s="2"/>
     </row>
-    <row r="503" ht="14.25" customHeight="1">
+    <row r="503" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C503" s="2"/>
     </row>
-    <row r="504" ht="14.25" customHeight="1">
+    <row r="504" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C504" s="2"/>
     </row>
-    <row r="505" ht="14.25" customHeight="1">
+    <row r="505" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C505" s="2"/>
     </row>
-    <row r="506" ht="14.25" customHeight="1">
+    <row r="506" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C506" s="2"/>
     </row>
-    <row r="507" ht="14.25" customHeight="1">
+    <row r="507" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C507" s="2"/>
     </row>
-    <row r="508" ht="14.25" customHeight="1">
+    <row r="508" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C508" s="2"/>
     </row>
-    <row r="509" ht="14.25" customHeight="1">
+    <row r="509" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C509" s="2"/>
     </row>
-    <row r="510" ht="14.25" customHeight="1">
+    <row r="510" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C510" s="2"/>
     </row>
-    <row r="511" ht="14.25" customHeight="1">
+    <row r="511" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C511" s="2"/>
     </row>
-    <row r="512" ht="14.25" customHeight="1">
+    <row r="512" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C512" s="2"/>
     </row>
-    <row r="513" ht="14.25" customHeight="1">
+    <row r="513" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C513" s="2"/>
     </row>
-    <row r="514" ht="14.25" customHeight="1">
+    <row r="514" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C514" s="2"/>
     </row>
-    <row r="515" ht="14.25" customHeight="1">
+    <row r="515" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C515" s="2"/>
     </row>
-    <row r="516" ht="14.25" customHeight="1">
+    <row r="516" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C516" s="2"/>
     </row>
-    <row r="517" ht="14.25" customHeight="1">
+    <row r="517" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C517" s="2"/>
     </row>
-    <row r="518" ht="14.25" customHeight="1">
+    <row r="518" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C518" s="2"/>
     </row>
-    <row r="519" ht="14.25" customHeight="1">
+    <row r="519" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C519" s="2"/>
     </row>
-    <row r="520" ht="14.25" customHeight="1">
+    <row r="520" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C520" s="2"/>
     </row>
-    <row r="521" ht="14.25" customHeight="1">
+    <row r="521" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C521" s="2"/>
     </row>
-    <row r="522" ht="14.25" customHeight="1">
+    <row r="522" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C522" s="2"/>
     </row>
-    <row r="523" ht="14.25" customHeight="1">
+    <row r="523" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C523" s="2"/>
     </row>
-    <row r="524" ht="14.25" customHeight="1">
+    <row r="524" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C524" s="2"/>
     </row>
-    <row r="525" ht="14.25" customHeight="1">
+    <row r="525" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C525" s="2"/>
     </row>
-    <row r="526" ht="14.25" customHeight="1">
+    <row r="526" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C526" s="2"/>
     </row>
-    <row r="527" ht="14.25" customHeight="1">
+    <row r="527" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C527" s="2"/>
     </row>
-    <row r="528" ht="14.25" customHeight="1">
+    <row r="528" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C528" s="2"/>
     </row>
-    <row r="529" ht="14.25" customHeight="1">
+    <row r="529" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C529" s="2"/>
     </row>
-    <row r="530" ht="14.25" customHeight="1">
+    <row r="530" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C530" s="2"/>
     </row>
-    <row r="531" ht="14.25" customHeight="1">
+    <row r="531" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C531" s="2"/>
     </row>
-    <row r="532" ht="14.25" customHeight="1">
+    <row r="532" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C532" s="2"/>
     </row>
-    <row r="533" ht="14.25" customHeight="1">
+    <row r="533" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C533" s="2"/>
     </row>
-    <row r="534" ht="14.25" customHeight="1">
+    <row r="534" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C534" s="2"/>
     </row>
-    <row r="535" ht="14.25" customHeight="1">
+    <row r="535" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C535" s="2"/>
     </row>
-    <row r="536" ht="14.25" customHeight="1">
+    <row r="536" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C536" s="2"/>
     </row>
-    <row r="537" ht="14.25" customHeight="1">
+    <row r="537" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C537" s="2"/>
     </row>
-    <row r="538" ht="14.25" customHeight="1">
+    <row r="538" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C538" s="2"/>
     </row>
-    <row r="539" ht="14.25" customHeight="1">
+    <row r="539" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C539" s="2"/>
     </row>
-    <row r="540" ht="14.25" customHeight="1">
+    <row r="540" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C540" s="2"/>
     </row>
-    <row r="541" ht="14.25" customHeight="1">
+    <row r="541" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C541" s="2"/>
     </row>
-    <row r="542" ht="14.25" customHeight="1">
+    <row r="542" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C542" s="2"/>
     </row>
-    <row r="543" ht="14.25" customHeight="1">
+    <row r="543" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C543" s="2"/>
     </row>
-    <row r="544" ht="14.25" customHeight="1">
+    <row r="544" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C544" s="2"/>
     </row>
-    <row r="545" ht="14.25" customHeight="1">
+    <row r="545" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C545" s="2"/>
     </row>
-    <row r="546" ht="14.25" customHeight="1">
+    <row r="546" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C546" s="2"/>
     </row>
-    <row r="547" ht="14.25" customHeight="1">
+    <row r="547" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C547" s="2"/>
     </row>
-    <row r="548" ht="14.25" customHeight="1">
+    <row r="548" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C548" s="2"/>
     </row>
-    <row r="549" ht="14.25" customHeight="1">
+    <row r="549" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C549" s="2"/>
     </row>
-    <row r="550" ht="14.25" customHeight="1">
+    <row r="550" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C550" s="2"/>
     </row>
-    <row r="551" ht="14.25" customHeight="1">
+    <row r="551" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C551" s="2"/>
     </row>
-    <row r="552" ht="14.25" customHeight="1">
+    <row r="552" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C552" s="2"/>
     </row>
-    <row r="553" ht="14.25" customHeight="1">
+    <row r="553" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C553" s="2"/>
     </row>
-    <row r="554" ht="14.25" customHeight="1">
+    <row r="554" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C554" s="2"/>
     </row>
-    <row r="555" ht="14.25" customHeight="1">
+    <row r="555" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C555" s="2"/>
     </row>
-    <row r="556" ht="14.25" customHeight="1">
+    <row r="556" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C556" s="2"/>
     </row>
-    <row r="557" ht="14.25" customHeight="1">
+    <row r="557" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C557" s="2"/>
     </row>
-    <row r="558" ht="14.25" customHeight="1">
+    <row r="558" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C558" s="2"/>
     </row>
-    <row r="559" ht="14.25" customHeight="1">
+    <row r="559" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C559" s="2"/>
     </row>
-    <row r="560" ht="14.25" customHeight="1">
+    <row r="560" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C560" s="2"/>
     </row>
-    <row r="561" ht="14.25" customHeight="1">
+    <row r="561" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C561" s="2"/>
     </row>
-    <row r="562" ht="14.25" customHeight="1">
+    <row r="562" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C562" s="2"/>
     </row>
-    <row r="563" ht="14.25" customHeight="1">
+    <row r="563" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C563" s="2"/>
     </row>
-    <row r="564" ht="14.25" customHeight="1">
+    <row r="564" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C564" s="2"/>
     </row>
-    <row r="565" ht="14.25" customHeight="1">
+    <row r="565" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C565" s="2"/>
     </row>
-    <row r="566" ht="14.25" customHeight="1">
+    <row r="566" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C566" s="2"/>
     </row>
-    <row r="567" ht="14.25" customHeight="1">
+    <row r="567" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C567" s="2"/>
     </row>
-    <row r="568" ht="14.25" customHeight="1">
+    <row r="568" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C568" s="2"/>
     </row>
-    <row r="569" ht="14.25" customHeight="1">
+    <row r="569" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C569" s="2"/>
     </row>
-    <row r="570" ht="14.25" customHeight="1">
+    <row r="570" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C570" s="2"/>
     </row>
-    <row r="571" ht="14.25" customHeight="1">
+    <row r="571" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C571" s="2"/>
     </row>
-    <row r="572" ht="14.25" customHeight="1">
+    <row r="572" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C572" s="2"/>
     </row>
-    <row r="573" ht="14.25" customHeight="1">
+    <row r="573" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C573" s="2"/>
     </row>
-    <row r="574" ht="14.25" customHeight="1">
+    <row r="574" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C574" s="2"/>
     </row>
-    <row r="575" ht="14.25" customHeight="1">
+    <row r="575" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C575" s="2"/>
     </row>
-    <row r="576" ht="14.25" customHeight="1">
+    <row r="576" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C576" s="2"/>
     </row>
-    <row r="577" ht="14.25" customHeight="1">
+    <row r="577" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C577" s="2"/>
     </row>
-    <row r="578" ht="14.25" customHeight="1">
+    <row r="578" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C578" s="2"/>
     </row>
-    <row r="579" ht="14.25" customHeight="1">
+    <row r="579" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C579" s="2"/>
     </row>
-    <row r="580" ht="14.25" customHeight="1">
+    <row r="580" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C580" s="2"/>
     </row>
-    <row r="581" ht="14.25" customHeight="1">
+    <row r="581" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C581" s="2"/>
     </row>
-    <row r="582" ht="14.25" customHeight="1">
+    <row r="582" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C582" s="2"/>
     </row>
-    <row r="583" ht="14.25" customHeight="1">
+    <row r="583" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C583" s="2"/>
     </row>
-    <row r="584" ht="14.25" customHeight="1">
+    <row r="584" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C584" s="2"/>
     </row>
-    <row r="585" ht="14.25" customHeight="1">
+    <row r="585" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C585" s="2"/>
     </row>
-    <row r="586" ht="14.25" customHeight="1">
+    <row r="586" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C586" s="2"/>
     </row>
-    <row r="587" ht="14.25" customHeight="1">
+    <row r="587" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C587" s="2"/>
     </row>
-    <row r="588" ht="14.25" customHeight="1">
+    <row r="588" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C588" s="2"/>
     </row>
-    <row r="589" ht="14.25" customHeight="1">
+    <row r="589" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C589" s="2"/>
     </row>
-    <row r="590" ht="14.25" customHeight="1">
+    <row r="590" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C590" s="2"/>
     </row>
-    <row r="591" ht="14.25" customHeight="1">
+    <row r="591" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C591" s="2"/>
     </row>
-    <row r="592" ht="14.25" customHeight="1">
+    <row r="592" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C592" s="2"/>
     </row>
-    <row r="593" ht="14.25" customHeight="1">
+    <row r="593" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C593" s="2"/>
     </row>
-    <row r="594" ht="14.25" customHeight="1">
+    <row r="594" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C594" s="2"/>
     </row>
-    <row r="595" ht="14.25" customHeight="1">
+    <row r="595" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C595" s="2"/>
     </row>
-    <row r="596" ht="14.25" customHeight="1">
+    <row r="596" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C596" s="2"/>
     </row>
-    <row r="597" ht="14.25" customHeight="1">
+    <row r="597" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C597" s="2"/>
     </row>
-    <row r="598" ht="14.25" customHeight="1">
+    <row r="598" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C598" s="2"/>
     </row>
-    <row r="599" ht="14.25" customHeight="1">
+    <row r="599" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C599" s="2"/>
     </row>
-    <row r="600" ht="14.25" customHeight="1">
+    <row r="600" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C600" s="2"/>
     </row>
-    <row r="601" ht="14.25" customHeight="1">
+    <row r="601" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C601" s="2"/>
     </row>
-    <row r="602" ht="14.25" customHeight="1">
+    <row r="602" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C602" s="2"/>
     </row>
-    <row r="603" ht="14.25" customHeight="1">
+    <row r="603" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C603" s="2"/>
     </row>
-    <row r="604" ht="14.25" customHeight="1">
+    <row r="604" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C604" s="2"/>
     </row>
-    <row r="605" ht="14.25" customHeight="1">
+    <row r="605" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C605" s="2"/>
     </row>
-    <row r="606" ht="14.25" customHeight="1">
+    <row r="606" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C606" s="2"/>
     </row>
-    <row r="607" ht="14.25" customHeight="1">
+    <row r="607" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C607" s="2"/>
     </row>
-    <row r="608" ht="14.25" customHeight="1">
+    <row r="608" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C608" s="2"/>
     </row>
-    <row r="609" ht="14.25" customHeight="1">
+    <row r="609" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C609" s="2"/>
     </row>
-    <row r="610" ht="14.25" customHeight="1">
+    <row r="610" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C610" s="2"/>
     </row>
-    <row r="611" ht="14.25" customHeight="1">
+    <row r="611" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C611" s="2"/>
     </row>
-    <row r="612" ht="14.25" customHeight="1">
+    <row r="612" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C612" s="2"/>
     </row>
-    <row r="613" ht="14.25" customHeight="1">
+    <row r="613" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C613" s="2"/>
     </row>
-    <row r="614" ht="14.25" customHeight="1">
+    <row r="614" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C614" s="2"/>
     </row>
-    <row r="615" ht="14.25" customHeight="1">
+    <row r="615" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C615" s="2"/>
     </row>
-    <row r="616" ht="14.25" customHeight="1">
+    <row r="616" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C616" s="2"/>
     </row>
-    <row r="617" ht="14.25" customHeight="1">
+    <row r="617" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C617" s="2"/>
     </row>
-    <row r="618" ht="14.25" customHeight="1">
+    <row r="618" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C618" s="2"/>
     </row>
-    <row r="619" ht="14.25" customHeight="1">
+    <row r="619" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C619" s="2"/>
     </row>
-    <row r="620" ht="14.25" customHeight="1">
+    <row r="620" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C620" s="2"/>
     </row>
-    <row r="621" ht="14.25" customHeight="1">
+    <row r="621" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C621" s="2"/>
     </row>
-    <row r="622" ht="14.25" customHeight="1">
+    <row r="622" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C622" s="2"/>
     </row>
-    <row r="623" ht="14.25" customHeight="1">
+    <row r="623" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C623" s="2"/>
     </row>
-    <row r="624" ht="14.25" customHeight="1">
+    <row r="624" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C624" s="2"/>
     </row>
-    <row r="625" ht="14.25" customHeight="1">
+    <row r="625" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C625" s="2"/>
     </row>
-    <row r="626" ht="14.25" customHeight="1">
+    <row r="626" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C626" s="2"/>
     </row>
-    <row r="627" ht="14.25" customHeight="1">
+    <row r="627" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C627" s="2"/>
     </row>
-    <row r="628" ht="14.25" customHeight="1">
+    <row r="628" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C628" s="2"/>
     </row>
-    <row r="629" ht="14.25" customHeight="1">
+    <row r="629" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C629" s="2"/>
     </row>
-    <row r="630" ht="14.25" customHeight="1">
+    <row r="630" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C630" s="2"/>
     </row>
-    <row r="631" ht="14.25" customHeight="1">
+    <row r="631" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C631" s="2"/>
     </row>
-    <row r="632" ht="14.25" customHeight="1">
+    <row r="632" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C632" s="2"/>
     </row>
-    <row r="633" ht="14.25" customHeight="1">
+    <row r="633" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C633" s="2"/>
     </row>
-    <row r="634" ht="14.25" customHeight="1">
+    <row r="634" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C634" s="2"/>
     </row>
-    <row r="635" ht="14.25" customHeight="1">
+    <row r="635" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C635" s="2"/>
     </row>
-    <row r="636" ht="14.25" customHeight="1">
+    <row r="636" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C636" s="2"/>
     </row>
-    <row r="637" ht="14.25" customHeight="1">
+    <row r="637" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C637" s="2"/>
     </row>
-    <row r="638" ht="14.25" customHeight="1">
+    <row r="638" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C638" s="2"/>
     </row>
-    <row r="639" ht="14.25" customHeight="1">
+    <row r="639" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C639" s="2"/>
     </row>
-    <row r="640" ht="14.25" customHeight="1">
+    <row r="640" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C640" s="2"/>
     </row>
-    <row r="641" ht="14.25" customHeight="1">
+    <row r="641" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C641" s="2"/>
     </row>
-    <row r="642" ht="14.25" customHeight="1">
+    <row r="642" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C642" s="2"/>
     </row>
-    <row r="643" ht="14.25" customHeight="1">
+    <row r="643" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C643" s="2"/>
     </row>
-    <row r="644" ht="14.25" customHeight="1">
+    <row r="644" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C644" s="2"/>
     </row>
-    <row r="645" ht="14.25" customHeight="1">
+    <row r="645" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C645" s="2"/>
     </row>
-    <row r="646" ht="14.25" customHeight="1">
+    <row r="646" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C646" s="2"/>
     </row>
-    <row r="647" ht="14.25" customHeight="1">
+    <row r="647" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C647" s="2"/>
     </row>
-    <row r="648" ht="14.25" customHeight="1">
+    <row r="648" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C648" s="2"/>
     </row>
-    <row r="649" ht="14.25" customHeight="1">
+    <row r="649" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C649" s="2"/>
     </row>
-    <row r="650" ht="14.25" customHeight="1">
+    <row r="650" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C650" s="2"/>
     </row>
-    <row r="651" ht="14.25" customHeight="1">
+    <row r="651" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C651" s="2"/>
     </row>
-    <row r="652" ht="14.25" customHeight="1">
+    <row r="652" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C652" s="2"/>
     </row>
-    <row r="653" ht="14.25" customHeight="1">
+    <row r="653" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C653" s="2"/>
     </row>
-    <row r="654" ht="14.25" customHeight="1">
+    <row r="654" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C654" s="2"/>
     </row>
-    <row r="655" ht="14.25" customHeight="1">
+    <row r="655" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C655" s="2"/>
     </row>
-    <row r="656" ht="14.25" customHeight="1">
+    <row r="656" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C656" s="2"/>
     </row>
-    <row r="657" ht="14.25" customHeight="1">
+    <row r="657" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C657" s="2"/>
     </row>
-    <row r="658" ht="14.25" customHeight="1">
+    <row r="658" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C658" s="2"/>
     </row>
-    <row r="659" ht="14.25" customHeight="1">
+    <row r="659" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C659" s="2"/>
     </row>
-    <row r="660" ht="14.25" customHeight="1">
+    <row r="660" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C660" s="2"/>
     </row>
-    <row r="661" ht="14.25" customHeight="1">
+    <row r="661" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C661" s="2"/>
     </row>
-    <row r="662" ht="14.25" customHeight="1">
+    <row r="662" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C662" s="2"/>
     </row>
-    <row r="663" ht="14.25" customHeight="1">
+    <row r="663" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C663" s="2"/>
     </row>
-    <row r="664" ht="14.25" customHeight="1">
+    <row r="664" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C664" s="2"/>
     </row>
-    <row r="665" ht="14.25" customHeight="1">
+    <row r="665" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C665" s="2"/>
     </row>
-    <row r="666" ht="14.25" customHeight="1">
+    <row r="666" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C666" s="2"/>
     </row>
-    <row r="667" ht="14.25" customHeight="1">
+    <row r="667" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C667" s="2"/>
     </row>
-    <row r="668" ht="14.25" customHeight="1">
+    <row r="668" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C668" s="2"/>
     </row>
-    <row r="669" ht="14.25" customHeight="1">
+    <row r="669" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C669" s="2"/>
     </row>
-    <row r="670" ht="14.25" customHeight="1">
+    <row r="670" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C670" s="2"/>
     </row>
-    <row r="671" ht="14.25" customHeight="1">
+    <row r="671" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C671" s="2"/>
     </row>
-    <row r="672" ht="14.25" customHeight="1">
+    <row r="672" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C672" s="2"/>
     </row>
-    <row r="673" ht="14.25" customHeight="1">
+    <row r="673" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C673" s="2"/>
     </row>
-    <row r="674" ht="14.25" customHeight="1">
+    <row r="674" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C674" s="2"/>
     </row>
-    <row r="675" ht="14.25" customHeight="1">
+    <row r="675" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C675" s="2"/>
     </row>
-    <row r="676" ht="14.25" customHeight="1">
+    <row r="676" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C676" s="2"/>
     </row>
-    <row r="677" ht="14.25" customHeight="1">
+    <row r="677" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C677" s="2"/>
     </row>
-    <row r="678" ht="14.25" customHeight="1">
+    <row r="678" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C678" s="2"/>
     </row>
-    <row r="679" ht="14.25" customHeight="1">
+    <row r="679" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C679" s="2"/>
     </row>
-    <row r="680" ht="14.25" customHeight="1">
+    <row r="680" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C680" s="2"/>
     </row>
-    <row r="681" ht="14.25" customHeight="1">
+    <row r="681" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C681" s="2"/>
     </row>
-    <row r="682" ht="14.25" customHeight="1">
+    <row r="682" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C682" s="2"/>
     </row>
-    <row r="683" ht="14.25" customHeight="1">
+    <row r="683" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C683" s="2"/>
     </row>
-    <row r="684" ht="14.25" customHeight="1">
+    <row r="684" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C684" s="2"/>
     </row>
-    <row r="685" ht="14.25" customHeight="1">
+    <row r="685" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C685" s="2"/>
     </row>
-    <row r="686" ht="14.25" customHeight="1">
+    <row r="686" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C686" s="2"/>
     </row>
-    <row r="687" ht="14.25" customHeight="1">
+    <row r="687" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C687" s="2"/>
     </row>
-    <row r="688" ht="14.25" customHeight="1">
+    <row r="688" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C688" s="2"/>
     </row>
-    <row r="689" ht="14.25" customHeight="1">
+    <row r="689" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C689" s="2"/>
     </row>
-    <row r="690" ht="14.25" customHeight="1">
+    <row r="690" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C690" s="2"/>
     </row>
-    <row r="691" ht="14.25" customHeight="1">
+    <row r="691" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C691" s="2"/>
     </row>
-    <row r="692" ht="14.25" customHeight="1">
+    <row r="692" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C692" s="2"/>
     </row>
-    <row r="693" ht="14.25" customHeight="1">
+    <row r="693" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C693" s="2"/>
     </row>
-    <row r="694" ht="14.25" customHeight="1">
+    <row r="694" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C694" s="2"/>
     </row>
-    <row r="695" ht="14.25" customHeight="1">
+    <row r="695" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C695" s="2"/>
     </row>
-    <row r="696" ht="14.25" customHeight="1">
+    <row r="696" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C696" s="2"/>
     </row>
-    <row r="697" ht="14.25" customHeight="1">
+    <row r="697" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C697" s="2"/>
     </row>
-    <row r="698" ht="14.25" customHeight="1">
+    <row r="698" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C698" s="2"/>
     </row>
-    <row r="699" ht="14.25" customHeight="1">
+    <row r="699" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C699" s="2"/>
     </row>
-    <row r="700" ht="14.25" customHeight="1">
+    <row r="700" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C700" s="2"/>
     </row>
-    <row r="701" ht="14.25" customHeight="1">
+    <row r="701" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C701" s="2"/>
     </row>
-    <row r="702" ht="14.25" customHeight="1">
+    <row r="702" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C702" s="2"/>
     </row>
-    <row r="703" ht="14.25" customHeight="1">
+    <row r="703" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C703" s="2"/>
     </row>
-    <row r="704" ht="14.25" customHeight="1">
+    <row r="704" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C704" s="2"/>
     </row>
-    <row r="705" ht="14.25" customHeight="1">
+    <row r="705" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C705" s="2"/>
     </row>
-    <row r="706" ht="14.25" customHeight="1">
+    <row r="706" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C706" s="2"/>
     </row>
-    <row r="707" ht="14.25" customHeight="1">
+    <row r="707" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C707" s="2"/>
     </row>
-    <row r="708" ht="14.25" customHeight="1">
+    <row r="708" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C708" s="2"/>
     </row>
-    <row r="709" ht="14.25" customHeight="1">
+    <row r="709" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C709" s="2"/>
     </row>
-    <row r="710" ht="14.25" customHeight="1">
+    <row r="710" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C710" s="2"/>
     </row>
-    <row r="711" ht="14.25" customHeight="1">
+    <row r="711" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C711" s="2"/>
     </row>
-    <row r="712" ht="14.25" customHeight="1">
+    <row r="712" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C712" s="2"/>
     </row>
-    <row r="713" ht="14.25" customHeight="1">
+    <row r="713" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C713" s="2"/>
     </row>
-    <row r="714" ht="14.25" customHeight="1">
+    <row r="714" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C714" s="2"/>
     </row>
-    <row r="715" ht="14.25" customHeight="1">
+    <row r="715" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C715" s="2"/>
     </row>
-    <row r="716" ht="14.25" customHeight="1">
+    <row r="716" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C716" s="2"/>
     </row>
-    <row r="717" ht="14.25" customHeight="1">
+    <row r="717" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C717" s="2"/>
     </row>
-    <row r="718" ht="14.25" customHeight="1">
+    <row r="718" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C718" s="2"/>
     </row>
-    <row r="719" ht="14.25" customHeight="1">
+    <row r="719" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C719" s="2"/>
     </row>
-    <row r="720" ht="14.25" customHeight="1">
+    <row r="720" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C720" s="2"/>
     </row>
-    <row r="721" ht="14.25" customHeight="1">
+    <row r="721" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C721" s="2"/>
     </row>
-    <row r="722" ht="14.25" customHeight="1">
+    <row r="722" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C722" s="2"/>
     </row>
-    <row r="723" ht="14.25" customHeight="1">
+    <row r="723" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C723" s="2"/>
     </row>
-    <row r="724" ht="14.25" customHeight="1">
+    <row r="724" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C724" s="2"/>
     </row>
-    <row r="725" ht="14.25" customHeight="1">
+    <row r="725" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C725" s="2"/>
     </row>
-    <row r="726" ht="14.25" customHeight="1">
+    <row r="726" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C726" s="2"/>
     </row>
-    <row r="727" ht="14.25" customHeight="1">
+    <row r="727" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C727" s="2"/>
     </row>
-    <row r="728" ht="14.25" customHeight="1">
+    <row r="728" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C728" s="2"/>
     </row>
-    <row r="729" ht="14.25" customHeight="1">
+    <row r="729" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C729" s="2"/>
     </row>
-    <row r="730" ht="14.25" customHeight="1">
+    <row r="730" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C730" s="2"/>
     </row>
-    <row r="731" ht="14.25" customHeight="1">
+    <row r="731" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C731" s="2"/>
     </row>
-    <row r="732" ht="14.25" customHeight="1">
+    <row r="732" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C732" s="2"/>
     </row>
-    <row r="733" ht="14.25" customHeight="1">
+    <row r="733" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C733" s="2"/>
     </row>
-    <row r="734" ht="14.25" customHeight="1">
+    <row r="734" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C734" s="2"/>
     </row>
-    <row r="735" ht="14.25" customHeight="1">
+    <row r="735" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C735" s="2"/>
     </row>
-    <row r="736" ht="14.25" customHeight="1">
+    <row r="736" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C736" s="2"/>
     </row>
-    <row r="737" ht="14.25" customHeight="1">
+    <row r="737" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C737" s="2"/>
     </row>
-    <row r="738" ht="14.25" customHeight="1">
+    <row r="738" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C738" s="2"/>
     </row>
-    <row r="739" ht="14.25" customHeight="1">
+    <row r="739" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C739" s="2"/>
     </row>
-    <row r="740" ht="14.25" customHeight="1">
+    <row r="740" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C740" s="2"/>
     </row>
-    <row r="741" ht="14.25" customHeight="1">
+    <row r="741" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C741" s="2"/>
     </row>
-    <row r="742" ht="14.25" customHeight="1">
+    <row r="742" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C742" s="2"/>
     </row>
-    <row r="743" ht="14.25" customHeight="1">
+    <row r="743" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C743" s="2"/>
     </row>
-    <row r="744" ht="14.25" customHeight="1">
+    <row r="744" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C744" s="2"/>
     </row>
-    <row r="745" ht="14.25" customHeight="1">
+    <row r="745" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C745" s="2"/>
     </row>
-    <row r="746" ht="14.25" customHeight="1">
+    <row r="746" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C746" s="2"/>
     </row>
-    <row r="747" ht="14.25" customHeight="1">
+    <row r="747" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C747" s="2"/>
     </row>
-    <row r="748" ht="14.25" customHeight="1">
+    <row r="748" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C748" s="2"/>
     </row>
-    <row r="749" ht="14.25" customHeight="1">
+    <row r="749" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C749" s="2"/>
     </row>
-    <row r="750" ht="14.25" customHeight="1">
+    <row r="750" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C750" s="2"/>
     </row>
-    <row r="751" ht="14.25" customHeight="1">
+    <row r="751" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C751" s="2"/>
     </row>
-    <row r="752" ht="14.25" customHeight="1">
+    <row r="752" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C752" s="2"/>
     </row>
-    <row r="753" ht="14.25" customHeight="1">
+    <row r="753" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C753" s="2"/>
     </row>
-    <row r="754" ht="14.25" customHeight="1">
+    <row r="754" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C754" s="2"/>
     </row>
-    <row r="755" ht="14.25" customHeight="1">
+    <row r="755" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C755" s="2"/>
     </row>
-    <row r="756" ht="14.25" customHeight="1">
+    <row r="756" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C756" s="2"/>
     </row>
-    <row r="757" ht="14.25" customHeight="1">
+    <row r="757" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C757" s="2"/>
     </row>
-    <row r="758" ht="14.25" customHeight="1">
+    <row r="758" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C758" s="2"/>
     </row>
-    <row r="759" ht="14.25" customHeight="1">
+    <row r="759" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C759" s="2"/>
     </row>
-    <row r="760" ht="14.25" customHeight="1">
+    <row r="760" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C760" s="2"/>
     </row>
-    <row r="761" ht="14.25" customHeight="1">
+    <row r="761" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C761" s="2"/>
     </row>
-    <row r="762" ht="14.25" customHeight="1">
+    <row r="762" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C762" s="2"/>
     </row>
-    <row r="763" ht="14.25" customHeight="1">
+    <row r="763" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C763" s="2"/>
     </row>
-    <row r="764" ht="14.25" customHeight="1">
+    <row r="764" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C764" s="2"/>
     </row>
-    <row r="765" ht="14.25" customHeight="1">
+    <row r="765" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C765" s="2"/>
     </row>
-    <row r="766" ht="14.25" customHeight="1">
+    <row r="766" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C766" s="2"/>
     </row>
-    <row r="767" ht="14.25" customHeight="1">
+    <row r="767" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C767" s="2"/>
     </row>
-    <row r="768" ht="14.25" customHeight="1">
+    <row r="768" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C768" s="2"/>
     </row>
-    <row r="769" ht="14.25" customHeight="1">
+    <row r="769" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C769" s="2"/>
     </row>
-    <row r="770" ht="14.25" customHeight="1">
+    <row r="770" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C770" s="2"/>
     </row>
-    <row r="771" ht="14.25" customHeight="1">
+    <row r="771" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C771" s="2"/>
     </row>
-    <row r="772" ht="14.25" customHeight="1">
+    <row r="772" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C772" s="2"/>
     </row>
-    <row r="773" ht="14.25" customHeight="1">
+    <row r="773" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C773" s="2"/>
     </row>
-    <row r="774" ht="14.25" customHeight="1">
+    <row r="774" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C774" s="2"/>
     </row>
-    <row r="775" ht="14.25" customHeight="1">
+    <row r="775" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C775" s="2"/>
     </row>
-    <row r="776" ht="14.25" customHeight="1">
+    <row r="776" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C776" s="2"/>
     </row>
-    <row r="777" ht="14.25" customHeight="1">
+    <row r="777" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C777" s="2"/>
     </row>
-    <row r="778" ht="14.25" customHeight="1">
+    <row r="778" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C778" s="2"/>
     </row>
-    <row r="779" ht="14.25" customHeight="1">
+    <row r="779" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C779" s="2"/>
     </row>
-    <row r="780" ht="14.25" customHeight="1">
+    <row r="780" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C780" s="2"/>
     </row>
-    <row r="781" ht="14.25" customHeight="1">
+    <row r="781" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C781" s="2"/>
     </row>
-    <row r="782" ht="14.25" customHeight="1">
+    <row r="782" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C782" s="2"/>
     </row>
-    <row r="783" ht="14.25" customHeight="1">
+    <row r="783" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C783" s="2"/>
     </row>
-    <row r="784" ht="14.25" customHeight="1">
+    <row r="784" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C784" s="2"/>
     </row>
-    <row r="785" ht="14.25" customHeight="1">
+    <row r="785" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C785" s="2"/>
     </row>
-    <row r="786" ht="14.25" customHeight="1">
+    <row r="786" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C786" s="2"/>
     </row>
-    <row r="787" ht="14.25" customHeight="1">
+    <row r="787" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C787" s="2"/>
     </row>
-    <row r="788" ht="14.25" customHeight="1">
+    <row r="788" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C788" s="2"/>
     </row>
-    <row r="789" ht="14.25" customHeight="1">
+    <row r="789" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C789" s="2"/>
     </row>
-    <row r="790" ht="14.25" customHeight="1">
+    <row r="790" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C790" s="2"/>
     </row>
-    <row r="791" ht="14.25" customHeight="1">
+    <row r="791" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C791" s="2"/>
     </row>
-    <row r="792" ht="14.25" customHeight="1">
+    <row r="792" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C792" s="2"/>
     </row>
-    <row r="793" ht="14.25" customHeight="1">
+    <row r="793" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C793" s="2"/>
     </row>
-    <row r="794" ht="14.25" customHeight="1">
+    <row r="794" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C794" s="2"/>
     </row>
-    <row r="795" ht="14.25" customHeight="1">
+    <row r="795" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C795" s="2"/>
     </row>
-    <row r="796" ht="14.25" customHeight="1">
+    <row r="796" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C796" s="2"/>
     </row>
-    <row r="797" ht="14.25" customHeight="1">
+    <row r="797" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C797" s="2"/>
     </row>
-    <row r="798" ht="14.25" customHeight="1">
+    <row r="798" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C798" s="2"/>
     </row>
-    <row r="799" ht="14.25" customHeight="1">
+    <row r="799" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C799" s="2"/>
     </row>
-    <row r="800" ht="14.25" customHeight="1">
+    <row r="800" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C800" s="2"/>
     </row>
-    <row r="801" ht="14.25" customHeight="1">
+    <row r="801" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C801" s="2"/>
     </row>
-    <row r="802" ht="14.25" customHeight="1">
+    <row r="802" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C802" s="2"/>
     </row>
-    <row r="803" ht="14.25" customHeight="1">
+    <row r="803" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C803" s="2"/>
     </row>
-    <row r="804" ht="14.25" customHeight="1">
+    <row r="804" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C804" s="2"/>
     </row>
-    <row r="805" ht="14.25" customHeight="1">
+    <row r="805" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C805" s="2"/>
     </row>
-    <row r="806" ht="14.25" customHeight="1">
+    <row r="806" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C806" s="2"/>
     </row>
-    <row r="807" ht="14.25" customHeight="1">
+    <row r="807" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C807" s="2"/>
     </row>
-    <row r="808" ht="14.25" customHeight="1">
+    <row r="808" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C808" s="2"/>
     </row>
-    <row r="809" ht="14.25" customHeight="1">
+    <row r="809" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C809" s="2"/>
     </row>
-    <row r="810" ht="14.25" customHeight="1">
+    <row r="810" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C810" s="2"/>
     </row>
-    <row r="811" ht="14.25" customHeight="1">
+    <row r="811" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C811" s="2"/>
     </row>
-    <row r="812" ht="14.25" customHeight="1">
+    <row r="812" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C812" s="2"/>
     </row>
-    <row r="813" ht="14.25" customHeight="1">
+    <row r="813" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C813" s="2"/>
     </row>
-    <row r="814" ht="14.25" customHeight="1">
+    <row r="814" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C814" s="2"/>
     </row>
-    <row r="815" ht="14.25" customHeight="1">
+    <row r="815" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C815" s="2"/>
     </row>
-    <row r="816" ht="14.25" customHeight="1">
+    <row r="816" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C816" s="2"/>
     </row>
-    <row r="817" ht="14.25" customHeight="1">
+    <row r="817" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C817" s="2"/>
     </row>
-    <row r="818" ht="14.25" customHeight="1">
+    <row r="818" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C818" s="2"/>
     </row>
-    <row r="819" ht="14.25" customHeight="1">
+    <row r="819" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C819" s="2"/>
     </row>
-    <row r="820" ht="14.25" customHeight="1">
+    <row r="820" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C820" s="2"/>
     </row>
-    <row r="821" ht="14.25" customHeight="1">
+    <row r="821" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C821" s="2"/>
     </row>
-    <row r="822" ht="14.25" customHeight="1">
+    <row r="822" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C822" s="2"/>
     </row>
-    <row r="823" ht="14.25" customHeight="1">
+    <row r="823" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C823" s="2"/>
     </row>
-    <row r="824" ht="14.25" customHeight="1">
+    <row r="824" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C824" s="2"/>
     </row>
-    <row r="825" ht="14.25" customHeight="1">
+    <row r="825" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C825" s="2"/>
     </row>
-    <row r="826" ht="14.25" customHeight="1">
+    <row r="826" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C826" s="2"/>
     </row>
-    <row r="827" ht="14.25" customHeight="1">
+    <row r="827" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C827" s="2"/>
     </row>
-    <row r="828" ht="14.25" customHeight="1">
+    <row r="828" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C828" s="2"/>
     </row>
-    <row r="829" ht="14.25" customHeight="1">
+    <row r="829" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C829" s="2"/>
     </row>
-    <row r="830" ht="14.25" customHeight="1">
+    <row r="830" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C830" s="2"/>
     </row>
-    <row r="831" ht="14.25" customHeight="1">
+    <row r="831" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C831" s="2"/>
     </row>
-    <row r="832" ht="14.25" customHeight="1">
+    <row r="832" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C832" s="2"/>
     </row>
-    <row r="833" ht="14.25" customHeight="1">
+    <row r="833" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C833" s="2"/>
     </row>
-    <row r="834" ht="14.25" customHeight="1">
+    <row r="834" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C834" s="2"/>
     </row>
-    <row r="835" ht="14.25" customHeight="1">
+    <row r="835" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C835" s="2"/>
     </row>
-    <row r="836" ht="14.25" customHeight="1">
+    <row r="836" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C836" s="2"/>
     </row>
-    <row r="837" ht="14.25" customHeight="1">
+    <row r="837" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C837" s="2"/>
     </row>
-    <row r="838" ht="14.25" customHeight="1">
+    <row r="838" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C838" s="2"/>
     </row>
-    <row r="839" ht="14.25" customHeight="1">
+    <row r="839" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C839" s="2"/>
     </row>
-    <row r="840" ht="14.25" customHeight="1">
+    <row r="840" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C840" s="2"/>
     </row>
-    <row r="841" ht="14.25" customHeight="1">
+    <row r="841" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C841" s="2"/>
     </row>
-    <row r="842" ht="14.25" customHeight="1">
+    <row r="842" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C842" s="2"/>
     </row>
-    <row r="843" ht="14.25" customHeight="1">
+    <row r="843" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C843" s="2"/>
     </row>
-    <row r="844" ht="14.25" customHeight="1">
+    <row r="844" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C844" s="2"/>
     </row>
-    <row r="845" ht="14.25" customHeight="1">
+    <row r="845" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C845" s="2"/>
     </row>
-    <row r="846" ht="14.25" customHeight="1">
+    <row r="846" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C846" s="2"/>
     </row>
-    <row r="847" ht="14.25" customHeight="1">
+    <row r="847" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C847" s="2"/>
     </row>
-    <row r="848" ht="14.25" customHeight="1">
+    <row r="848" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C848" s="2"/>
     </row>
-    <row r="849" ht="14.25" customHeight="1">
+    <row r="849" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C849" s="2"/>
     </row>
-    <row r="850" ht="14.25" customHeight="1">
+    <row r="850" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C850" s="2"/>
     </row>
-    <row r="851" ht="14.25" customHeight="1">
+    <row r="851" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C851" s="2"/>
     </row>
-    <row r="852" ht="14.25" customHeight="1">
+    <row r="852" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C852" s="2"/>
     </row>
-    <row r="853" ht="14.25" customHeight="1">
+    <row r="853" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C853" s="2"/>
     </row>
-    <row r="854" ht="14.25" customHeight="1">
+    <row r="854" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C854" s="2"/>
     </row>
-    <row r="855" ht="14.25" customHeight="1">
+    <row r="855" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C855" s="2"/>
     </row>
-    <row r="856" ht="14.25" customHeight="1">
+    <row r="856" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C856" s="2"/>
     </row>
-    <row r="857" ht="14.25" customHeight="1">
+    <row r="857" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C857" s="2"/>
     </row>
-    <row r="858" ht="14.25" customHeight="1">
+    <row r="858" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C858" s="2"/>
     </row>
-    <row r="859" ht="14.25" customHeight="1">
+    <row r="859" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C859" s="2"/>
     </row>
-    <row r="860" ht="14.25" customHeight="1">
+    <row r="860" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C860" s="2"/>
     </row>
-    <row r="861" ht="14.25" customHeight="1">
+    <row r="861" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C861" s="2"/>
     </row>
-    <row r="862" ht="14.25" customHeight="1">
+    <row r="862" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C862" s="2"/>
     </row>
-    <row r="863" ht="14.25" customHeight="1">
+    <row r="863" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C863" s="2"/>
     </row>
-    <row r="864" ht="14.25" customHeight="1">
+    <row r="864" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C864" s="2"/>
     </row>
-    <row r="865" ht="14.25" customHeight="1">
+    <row r="865" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C865" s="2"/>
     </row>
-    <row r="866" ht="14.25" customHeight="1">
+    <row r="866" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C866" s="2"/>
     </row>
-    <row r="867" ht="14.25" customHeight="1">
+    <row r="867" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C867" s="2"/>
     </row>
-    <row r="868" ht="14.25" customHeight="1">
+    <row r="868" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C868" s="2"/>
     </row>
-    <row r="869" ht="14.25" customHeight="1">
+    <row r="869" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C869" s="2"/>
     </row>
-    <row r="870" ht="14.25" customHeight="1">
+    <row r="870" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C870" s="2"/>
     </row>
-    <row r="871" ht="14.25" customHeight="1">
+    <row r="871" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C871" s="2"/>
     </row>
-    <row r="872" ht="14.25" customHeight="1">
+    <row r="872" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C872" s="2"/>
     </row>
-    <row r="873" ht="14.25" customHeight="1">
+    <row r="873" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C873" s="2"/>
     </row>
-    <row r="874" ht="14.25" customHeight="1">
+    <row r="874" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C874" s="2"/>
     </row>
-    <row r="875" ht="14.25" customHeight="1">
+    <row r="875" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C875" s="2"/>
     </row>
-    <row r="876" ht="14.25" customHeight="1">
+    <row r="876" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C876" s="2"/>
     </row>
-    <row r="877" ht="14.25" customHeight="1">
+    <row r="877" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C877" s="2"/>
     </row>
-    <row r="878" ht="14.25" customHeight="1">
+    <row r="878" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C878" s="2"/>
     </row>
-    <row r="879" ht="14.25" customHeight="1">
+    <row r="879" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C879" s="2"/>
     </row>
-    <row r="880" ht="14.25" customHeight="1">
+    <row r="880" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C880" s="2"/>
     </row>
-    <row r="881" ht="14.25" customHeight="1">
+    <row r="881" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C881" s="2"/>
     </row>
-    <row r="882" ht="14.25" customHeight="1">
+    <row r="882" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C882" s="2"/>
     </row>
-    <row r="883" ht="14.25" customHeight="1">
+    <row r="883" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C883" s="2"/>
     </row>
-    <row r="884" ht="14.25" customHeight="1">
+    <row r="884" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C884" s="2"/>
     </row>
-    <row r="885" ht="14.25" customHeight="1">
+    <row r="885" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C885" s="2"/>
     </row>
-    <row r="886" ht="14.25" customHeight="1">
+    <row r="886" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C886" s="2"/>
     </row>
-    <row r="887" ht="14.25" customHeight="1">
+    <row r="887" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C887" s="2"/>
     </row>
-    <row r="888" ht="14.25" customHeight="1">
+    <row r="888" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C888" s="2"/>
     </row>
-    <row r="889" ht="14.25" customHeight="1">
+    <row r="889" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C889" s="2"/>
     </row>
-    <row r="890" ht="14.25" customHeight="1">
+    <row r="890" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C890" s="2"/>
     </row>
-    <row r="891" ht="14.25" customHeight="1">
+    <row r="891" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C891" s="2"/>
     </row>
-    <row r="892" ht="14.25" customHeight="1">
+    <row r="892" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C892" s="2"/>
     </row>
-    <row r="893" ht="14.25" customHeight="1">
+    <row r="893" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C893" s="2"/>
     </row>
-    <row r="894" ht="14.25" customHeight="1">
+    <row r="894" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C894" s="2"/>
     </row>
-    <row r="895" ht="14.25" customHeight="1">
+    <row r="895" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C895" s="2"/>
     </row>
-    <row r="896" ht="14.25" customHeight="1">
+    <row r="896" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C896" s="2"/>
     </row>
-    <row r="897" ht="14.25" customHeight="1">
+    <row r="897" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C897" s="2"/>
     </row>
-    <row r="898" ht="14.25" customHeight="1">
+    <row r="898" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C898" s="2"/>
     </row>
-    <row r="899" ht="14.25" customHeight="1">
+    <row r="899" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C899" s="2"/>
     </row>
-    <row r="900" ht="14.25" customHeight="1">
+    <row r="900" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C900" s="2"/>
     </row>
-    <row r="901" ht="14.25" customHeight="1">
+    <row r="901" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C901" s="2"/>
     </row>
-    <row r="902" ht="14.25" customHeight="1">
+    <row r="902" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C902" s="2"/>
     </row>
-    <row r="903" ht="14.25" customHeight="1">
+    <row r="903" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C903" s="2"/>
     </row>
-    <row r="904" ht="14.25" customHeight="1">
+    <row r="904" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C904" s="2"/>
     </row>
-    <row r="905" ht="14.25" customHeight="1">
+    <row r="905" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C905" s="2"/>
     </row>
-    <row r="906" ht="14.25" customHeight="1">
+    <row r="906" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C906" s="2"/>
     </row>
-    <row r="907" ht="14.25" customHeight="1">
+    <row r="907" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C907" s="2"/>
     </row>
-    <row r="908" ht="14.25" customHeight="1">
+    <row r="908" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C908" s="2"/>
     </row>
-    <row r="909" ht="14.25" customHeight="1">
+    <row r="909" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C909" s="2"/>
     </row>
-    <row r="910" ht="14.25" customHeight="1">
+    <row r="910" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C910" s="2"/>
     </row>
-    <row r="911" ht="14.25" customHeight="1">
+    <row r="911" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C911" s="2"/>
     </row>
-    <row r="912" ht="14.25" customHeight="1">
+    <row r="912" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C912" s="2"/>
     </row>
-    <row r="913" ht="14.25" customHeight="1">
+    <row r="913" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C913" s="2"/>
     </row>
-    <row r="914" ht="14.25" customHeight="1">
+    <row r="914" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C914" s="2"/>
     </row>
-    <row r="915" ht="14.25" customHeight="1">
+    <row r="915" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C915" s="2"/>
     </row>
-    <row r="916" ht="14.25" customHeight="1">
+    <row r="916" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C916" s="2"/>
     </row>
-    <row r="917" ht="14.25" customHeight="1">
+    <row r="917" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C917" s="2"/>
     </row>
-    <row r="918" ht="14.25" customHeight="1">
+    <row r="918" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C918" s="2"/>
     </row>
-    <row r="919" ht="14.25" customHeight="1">
+    <row r="919" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C919" s="2"/>
     </row>
-    <row r="920" ht="14.25" customHeight="1">
+    <row r="920" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C920" s="2"/>
     </row>
-    <row r="921" ht="14.25" customHeight="1">
+    <row r="921" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C921" s="2"/>
     </row>
-    <row r="922" ht="14.25" customHeight="1">
+    <row r="922" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C922" s="2"/>
     </row>
-    <row r="923" ht="14.25" customHeight="1">
+    <row r="923" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C923" s="2"/>
     </row>
-    <row r="924" ht="14.25" customHeight="1">
+    <row r="924" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C924" s="2"/>
     </row>
-    <row r="925" ht="14.25" customHeight="1">
+    <row r="925" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C925" s="2"/>
     </row>
-    <row r="926" ht="14.25" customHeight="1">
+    <row r="926" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C926" s="2"/>
     </row>
-    <row r="927" ht="14.25" customHeight="1">
+    <row r="927" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C927" s="2"/>
     </row>
-    <row r="928" ht="14.25" customHeight="1">
+    <row r="928" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C928" s="2"/>
     </row>
-    <row r="929" ht="14.25" customHeight="1">
+    <row r="929" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C929" s="2"/>
     </row>
-    <row r="930" ht="14.25" customHeight="1">
+    <row r="930" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C930" s="2"/>
     </row>
-    <row r="931" ht="14.25" customHeight="1">
+    <row r="931" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C931" s="2"/>
     </row>
-    <row r="932" ht="14.25" customHeight="1">
+    <row r="932" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C932" s="2"/>
     </row>
-    <row r="933" ht="14.25" customHeight="1">
+    <row r="933" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C933" s="2"/>
     </row>
-    <row r="934" ht="14.25" customHeight="1">
+    <row r="934" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C934" s="2"/>
     </row>
-    <row r="935" ht="14.25" customHeight="1">
+    <row r="935" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C935" s="2"/>
     </row>
-    <row r="936" ht="14.25" customHeight="1">
+    <row r="936" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C936" s="2"/>
     </row>
-    <row r="937" ht="14.25" customHeight="1">
+    <row r="937" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C937" s="2"/>
     </row>
-    <row r="938" ht="14.25" customHeight="1">
+    <row r="938" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C938" s="2"/>
     </row>
-    <row r="939" ht="14.25" customHeight="1">
+    <row r="939" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C939" s="2"/>
     </row>
-    <row r="940" ht="14.25" customHeight="1">
+    <row r="940" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C940" s="2"/>
     </row>
-    <row r="941" ht="14.25" customHeight="1">
+    <row r="941" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C941" s="2"/>
     </row>
-    <row r="942" ht="14.25" customHeight="1">
+    <row r="942" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C942" s="2"/>
     </row>
-    <row r="943" ht="14.25" customHeight="1">
+    <row r="943" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C943" s="2"/>
     </row>
-    <row r="944" ht="14.25" customHeight="1">
+    <row r="944" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C944" s="2"/>
     </row>
-    <row r="945" ht="14.25" customHeight="1">
+    <row r="945" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C945" s="2"/>
     </row>
-    <row r="946" ht="14.25" customHeight="1">
+    <row r="946" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C946" s="2"/>
     </row>
-    <row r="947" ht="14.25" customHeight="1">
+    <row r="947" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C947" s="2"/>
     </row>
-    <row r="948" ht="14.25" customHeight="1">
+    <row r="948" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C948" s="2"/>
     </row>
-    <row r="949" ht="14.25" customHeight="1">
+    <row r="949" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C949" s="2"/>
     </row>
-    <row r="950" ht="14.25" customHeight="1">
+    <row r="950" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C950" s="2"/>
     </row>
-    <row r="951" ht="14.25" customHeight="1">
+    <row r="951" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C951" s="2"/>
     </row>
-    <row r="952" ht="14.25" customHeight="1">
+    <row r="952" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C952" s="2"/>
     </row>
-    <row r="953" ht="14.25" customHeight="1">
+    <row r="953" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C953" s="2"/>
     </row>
-    <row r="954" ht="14.25" customHeight="1">
+    <row r="954" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C954" s="2"/>
     </row>
-    <row r="955" ht="14.25" customHeight="1">
+    <row r="955" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C955" s="2"/>
     </row>
-    <row r="956" ht="14.25" customHeight="1">
+    <row r="956" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C956" s="2"/>
     </row>
-    <row r="957" ht="14.25" customHeight="1">
+    <row r="957" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C957" s="2"/>
     </row>
-    <row r="958" ht="14.25" customHeight="1">
+    <row r="958" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C958" s="2"/>
     </row>
-    <row r="959" ht="14.25" customHeight="1">
+    <row r="959" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C959" s="2"/>
     </row>
-    <row r="960" ht="14.25" customHeight="1">
+    <row r="960" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C960" s="2"/>
     </row>
-    <row r="961" ht="14.25" customHeight="1">
+    <row r="961" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C961" s="2"/>
     </row>
-    <row r="962" ht="14.25" customHeight="1">
+    <row r="962" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C962" s="2"/>
     </row>
-    <row r="963" ht="14.25" customHeight="1">
+    <row r="963" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C963" s="2"/>
     </row>
-    <row r="964" ht="14.25" customHeight="1">
+    <row r="964" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C964" s="2"/>
     </row>
-    <row r="965" ht="14.25" customHeight="1">
+    <row r="965" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C965" s="2"/>
     </row>
-    <row r="966" ht="14.25" customHeight="1">
+    <row r="966" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C966" s="2"/>
     </row>
-    <row r="967" ht="14.25" customHeight="1">
+    <row r="967" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C967" s="2"/>
     </row>
-    <row r="968" ht="14.25" customHeight="1">
+    <row r="968" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C968" s="2"/>
     </row>
-    <row r="969" ht="14.25" customHeight="1">
+    <row r="969" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C969" s="2"/>
     </row>
-    <row r="970" ht="14.25" customHeight="1">
+    <row r="970" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C970" s="2"/>
     </row>
-    <row r="971" ht="14.25" customHeight="1">
+    <row r="971" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C971" s="2"/>
     </row>
-    <row r="972" ht="14.25" customHeight="1">
+    <row r="972" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C972" s="2"/>
     </row>
-    <row r="973" ht="14.25" customHeight="1">
+    <row r="973" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C973" s="2"/>
     </row>
-    <row r="974" ht="14.25" customHeight="1">
+    <row r="974" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C974" s="2"/>
     </row>
-    <row r="975" ht="14.25" customHeight="1">
+    <row r="975" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C975" s="2"/>
     </row>
-    <row r="976" ht="14.25" customHeight="1">
+    <row r="976" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C976" s="2"/>
     </row>
-    <row r="977" ht="14.25" customHeight="1">
+    <row r="977" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C977" s="2"/>
     </row>
-    <row r="978" ht="14.25" customHeight="1">
+    <row r="978" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C978" s="2"/>
     </row>
-    <row r="979" ht="14.25" customHeight="1">
+    <row r="979" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C979" s="2"/>
     </row>
-    <row r="980" ht="14.25" customHeight="1">
+    <row r="980" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C980" s="2"/>
     </row>
-    <row r="981" ht="14.25" customHeight="1">
+    <row r="981" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C981" s="2"/>
     </row>
-    <row r="982" ht="14.25" customHeight="1">
+    <row r="982" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C982" s="2"/>
     </row>
-    <row r="983" ht="14.25" customHeight="1">
+    <row r="983" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C983" s="2"/>
     </row>
-    <row r="984" ht="14.25" customHeight="1">
+    <row r="984" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C984" s="2"/>
     </row>
-    <row r="985" ht="14.25" customHeight="1">
+    <row r="985" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C985" s="2"/>
     </row>
-    <row r="986" ht="14.25" customHeight="1">
+    <row r="986" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C986" s="2"/>
     </row>
-    <row r="987" ht="14.25" customHeight="1">
+    <row r="987" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C987" s="2"/>
     </row>
-    <row r="988" ht="14.25" customHeight="1">
+    <row r="988" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C988" s="2"/>
     </row>
-    <row r="989" ht="14.25" customHeight="1">
+    <row r="989" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C989" s="2"/>
     </row>
-    <row r="990" ht="14.25" customHeight="1">
+    <row r="990" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C990" s="2"/>
     </row>
-    <row r="991" ht="14.25" customHeight="1">
+    <row r="991" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C991" s="2"/>
     </row>
-    <row r="992" ht="14.25" customHeight="1">
+    <row r="992" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C992" s="2"/>
     </row>
-    <row r="993" ht="14.25" customHeight="1">
+    <row r="993" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C993" s="2"/>
     </row>
-    <row r="994" ht="14.25" customHeight="1">
+    <row r="994" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C994" s="2"/>
     </row>
-    <row r="995" ht="14.25" customHeight="1">
+    <row r="995" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C995" s="2"/>
     </row>
-    <row r="996" ht="14.25" customHeight="1">
+    <row r="996" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C996" s="2"/>
     </row>
-    <row r="997" ht="14.25" customHeight="1">
+    <row r="997" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C997" s="2"/>
     </row>
-    <row r="998" ht="14.25" customHeight="1">
+    <row r="998" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C998" s="2"/>
     </row>
-    <row r="999" ht="14.25" customHeight="1">
+    <row r="999" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C999" s="2"/>
     </row>
-    <row r="1000" ht="14.25" customHeight="1">
+    <row r="1000" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C1000" s="2"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>